--- a/products_db.xlsx
+++ b/products_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1142"/>
+  <dimension ref="A1:C1148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19823,6 +19823,113 @@
         </is>
       </c>
     </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>แรงกว่าเดิมหัวกวนน้ำยาตัวกวนน้ำยาในถังพ่นยาพร้อมสายสวนเลือกขนาดได้</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>เฉพาะตัวกวนแอร์บัส</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>เฉพาะตัวกวนแอร์บัสdasdasdasdadasda
+dsaaaaaaaaaaaaaaaaaaadsadasdasdsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>ปั๊มพ่นยาแรงดันสูงพ่นยาติดเครื่องยนต์ปั๊ม3สูบพ่นยาปั๊มพ่นยาเกษตรสายพ่นยา 5 ชั้นแรงดันสูง</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>*ให้ร้านประกอบให้พร้อมใช้งาน</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>sadsadsadadadasdas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>ปั๊มพ่นยา 3 สูบติดเครื่องยนต์ 8.5 แรงปั๊มพ่นยา</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>6หุน*หม้อลมทูอินวัน</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>eqweqwewqeqeqw
+dsadasd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>สายพ่นยา 5 ชั้นแรงดันสูง 100/50 เมตรแถมฟรี *หัวฟรียอย* ทนแรงดันสูงสายพ่นยาต่อเครื่องพ่นยาหัวทองเหลืองแท้สายพ่นยา 5 ชั้นแรงดันสูง</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>100 เมตรพรีเมียมแถมหัวฟรียอย</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>100 เมตร พรีเมียมฟหก
+กฟหกฟก</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>ปั๊มพ่นยา 3 สูบติดเครื่องยนต์ 8.5 แรงปั๊มพ่นยาปั๊มพ่นยาแรงดันสูงพ่นยาติดเครื่องยนต์ปั๊ม3สูบพ่นยาปั๊มพ่นยาเกษตรสายพ่นยา 5 ชั้นแรงดันสูง</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>6หุน*หม้อลมทูอินวัน *ให้ร้านประกอบให้พร้อมใช้งาน</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>sadsadsadadadasdas
+dsadasdad</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>100/50 เมตรแถมฟรี *หัวฟรียอย* ทนแรงดันสูงสายพ่นยาต่อเครื่องพ่นยาหัวทองเหลืองแท้</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>100 เมตรพรีเมียมแถมหัวฟรียอย</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>100 เมตร พรีเมียม แถมหัวฟรียอย
+กฟหกหฟ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
